--- a/docs/roles_v2.xlsx
+++ b/docs/roles_v2.xlsx
@@ -2044,7 +2044,7 @@
           <t>❌</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -2071,7 +2071,7 @@
           <t>❌</t>
         </is>
       </c>
-      <c r="D55" s="6" t="inlineStr">
+      <c r="D55" s="4" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
@@ -2125,7 +2125,7 @@
           <t>❌</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D57" s="6" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
@@ -2152,7 +2152,7 @@
           <t>❌</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr">
+      <c r="D58" s="6" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
@@ -2179,7 +2179,7 @@
           <t>❌</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="D59" s="6" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
@@ -2206,7 +2206,7 @@
           <t>❌</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="D60" s="6" t="inlineStr">
         <is>
           <t>❌</t>
         </is>
@@ -2704,17 +2704,17 @@
   <mergeCells count="14">
     <mergeCell ref="A21:E21"/>
     <mergeCell ref="A53:E53"/>
-    <mergeCell ref="A77:E77"/>
-    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="A70:E70"/>
     <mergeCell ref="A43:E43"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="B75:E75"/>
-    <mergeCell ref="B73:E73"/>
+    <mergeCell ref="B80:E80"/>
+    <mergeCell ref="B78:E78"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="B74:E74"/>
+    <mergeCell ref="B79:E79"/>
     <mergeCell ref="A33:E33"/>
     <mergeCell ref="A47:E47"/>
-    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A63:E63"/>
     <mergeCell ref="A27:E27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
